--- a/output/changelog.xlsx
+++ b/output/changelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/pgallego_ic_ac_uk/Documents/PhD/Repositories/energy_reserve/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3687" documentId="13_ncr:1_{27CD5DFD-1054-4A33-AFFE-F35EA43968A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{849FC2D9-EF04-45CE-96F6-CE31022F4A2D}"/>
+  <xr:revisionPtr revIDLastSave="3696" documentId="13_ncr:1_{27CD5DFD-1054-4A33-AFFE-F35EA43968A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A72AD55D-9B9E-4104-87C1-9C41D55F1860}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="changelog input" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="1422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2542" uniqueCount="1425">
   <si>
     <t>:base_ramp_storage_reserve
 :base_ramp_storage_envelopes
@@ -5250,30 +5250,42 @@
 configuration_envelopes_e_reserve_mu_v2</t>
   </si>
   <si>
+    <t>32.3s</t>
+  </si>
+  <si>
+    <t>4d26af57c</t>
+  </si>
+  <si>
+    <t>envelope
+configuration_envelopes_e_reserve_mu_v3</t>
+  </si>
+  <si>
+    <t>repo</t>
+  </si>
+  <si>
+    <t>RTS-GMLC_v2.1.3</t>
+  </si>
+  <si>
+    <t>net_demand = load</t>
+  </si>
+  <si>
     <t>from 2.4.1
 Renamed CSP and hydro reservoir asset resources
-configuration_envelopes_e_reserve_mu =  multiplier calculated based on Ax=B with B = max_{i&lt;=t} ER_{i,t}
+configuration_envelopes_e_reserve_mu =  multiplier calculated based on Ax=B with B = max_{i&lt;=t} ER_{i,t
 configuration_envelopes_e_reserve_mu_v2 =  multiplier calculated based on Ax=B with B = ER_{1,t}
-configuration_envelopes_e_reserve_mu_v3 =  multiplier calculated based on Ax=B with B = ER_{1,t} and clip[0,1]</t>
-  </si>
-  <si>
-    <t>32.3s</t>
-  </si>
-  <si>
-    <t>4d26af57c</t>
+configuration_envelopes_e_reserve_mu_v3 =  multiplier calculated based on Ax=B with B = ER_{1,t} and clip[0,1] --&gt; e_reserve_mu.py
+configuration_envelopes_cumulative_reserve_mu_v1.csv =  multiplier based on cumulative imbalance over reserves metodology -&gt; cumulative_reserve_mu.py. Multiplier as a function of time
+configuration_envelopes_cumulative_reserve_mu_v2.csv =  multiplier based on cumulative imbalance over reserves metodology -&gt; cumulative_reserve_mu.py. Multiplier as last hour's value from previous</t>
+  </si>
+  <si>
+    <t>32.4s</t>
+  </si>
+  <si>
+    <t>ab414</t>
   </si>
   <si>
     <t>envelope
-configuration_envelopes_e_reserve_mu_v3</t>
-  </si>
-  <si>
-    <t>repo</t>
-  </si>
-  <si>
-    <t>RTS-GMLC_v2.1.3</t>
-  </si>
-  <si>
-    <t>net_demand = load</t>
+configuration_envelopes_cumulative_reserve_mu_v2</t>
   </si>
 </sst>
 </file>
@@ -5553,10 +5565,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6200,10 +6208,10 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C47" s="11" t="s">
         <v>1420</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="90" x14ac:dyDescent="0.25">
@@ -6246,15 +6254,15 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B53" s="43" t="s">
         <v>1361</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -6267,7 +6275,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B55" s="43" t="s">
         <v>1257</v>
@@ -15808,24 +15816,32 @@
     </row>
     <row r="580" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A580" s="15" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B580" s="13" t="s">
         <v>1361</v>
       </c>
       <c r="C580" s="13" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D580" s="25" t="s">
         <v>1417</v>
       </c>
-      <c r="D580" s="25" t="s">
-        <v>1418</v>
-      </c>
       <c r="E580" s="13"/>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A581" s="13"/>
-      <c r="B581" s="13"/>
-      <c r="C581" s="13"/>
-      <c r="D581" s="14"/>
+    <row r="581" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A581" s="13" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B581" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C581" s="13" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D581" s="25" t="s">
+        <v>1424</v>
+      </c>
       <c r="E581" s="13"/>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">

--- a/output/changelog.xlsx
+++ b/output/changelog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/pgallego_ic_ac_uk/Documents/PhD/Repositories/energy_reserve/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3696" documentId="13_ncr:1_{27CD5DFD-1054-4A33-AFFE-F35EA43968A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A72AD55D-9B9E-4104-87C1-9C41D55F1860}"/>
+  <xr:revisionPtr revIDLastSave="3719" documentId="13_ncr:1_{27CD5DFD-1054-4A33-AFFE-F35EA43968A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E17E638-69C8-43AE-9956-299EA560E25F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2542" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1430">
   <si>
     <t>:base_ramp_storage_reserve
 :base_ramp_storage_envelopes
@@ -5269,30 +5269,48 @@
     <t>net_demand = load</t>
   </si>
   <si>
+    <t>32.4s</t>
+  </si>
+  <si>
+    <t>ab414</t>
+  </si>
+  <si>
+    <t>envelope
+configuration_envelopes_cumulative_reserve_mu_v2</t>
+  </si>
+  <si>
+    <t>envelope
+configuration_envelopes_sensitivity_mu_v1</t>
+  </si>
+  <si>
+    <t>32.5s</t>
+  </si>
+  <si>
+    <t>32.6s</t>
+  </si>
+  <si>
+    <t>envelope
+configuration_envelopes_cumulative_reserve_mu_v1.1 (</t>
+  </si>
+  <si>
     <t>from 2.4.1
 Renamed CSP and hydro reservoir asset resources
 configuration_envelopes_e_reserve_mu =  multiplier calculated based on Ax=B with B = max_{i&lt;=t} ER_{i,t
 configuration_envelopes_e_reserve_mu_v2 =  multiplier calculated based on Ax=B with B = ER_{1,t}
 configuration_envelopes_e_reserve_mu_v3 =  multiplier calculated based on Ax=B with B = ER_{1,t} and clip[0,1] --&gt; e_reserve_mu.py
 configuration_envelopes_cumulative_reserve_mu_v1.csv =  multiplier based on cumulative imbalance over reserves metodology -&gt; cumulative_reserve_mu.py. Multiplier as a function of time
+configuration_envelopes_cumulative_reserve_mu_v1.1.csv  = previos values caped by 1
 configuration_envelopes_cumulative_reserve_mu_v2.csv =  multiplier based on cumulative imbalance over reserves metodology -&gt; cumulative_reserve_mu.py. Multiplier as last hour's value from previous</t>
   </si>
   <si>
-    <t>32.4s</t>
-  </si>
-  <si>
-    <t>ab414</t>
-  </si>
-  <si>
-    <t>envelope
-configuration_envelopes_cumulative_reserve_mu_v2</t>
+    <t>To be added</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5384,6 +5402,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -5436,7 +5461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -5549,6 +5574,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6102,7 +6128,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>802</v>
       </c>
@@ -6110,7 +6136,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>840</v>
       </c>
@@ -6118,7 +6144,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>971</v>
       </c>
@@ -6126,7 +6152,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>864</v>
       </c>
@@ -6134,7 +6160,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>865</v>
       </c>
@@ -6142,7 +6168,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>868</v>
       </c>
@@ -6150,7 +6176,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>870</v>
       </c>
@@ -6158,7 +6184,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>876</v>
       </c>
@@ -6166,7 +6192,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>878</v>
       </c>
@@ -6174,7 +6200,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>880</v>
       </c>
@@ -6182,7 +6208,10 @@
         <v>973</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A44" s="44" t="s">
+        <v>1429</v>
+      </c>
       <c r="B44" t="s">
         <v>891</v>
       </c>
@@ -6190,7 +6219,10 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="44" t="s">
+        <v>1429</v>
+      </c>
       <c r="B45" t="s">
         <v>921</v>
       </c>
@@ -6198,7 +6230,10 @@
         <v>924</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="44" t="s">
+        <v>1429</v>
+      </c>
       <c r="B46" t="s">
         <v>922</v>
       </c>
@@ -6206,7 +6241,10 @@
         <v>923</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="44" t="s">
+        <v>1429</v>
+      </c>
       <c r="B47" t="s">
         <v>1419</v>
       </c>
@@ -6214,7 +6252,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>1087</v>
       </c>
@@ -6254,7 +6292,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="165" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1418</v>
       </c>
@@ -6262,7 +6300,7 @@
         <v>1361</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -6422,7 +6460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q966"/>
+  <dimension ref="A1:Q967"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.140625" customWidth="1"/>
@@ -15831,38 +15869,50 @@
     </row>
     <row r="581" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A581" s="13" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B581" s="13" t="s">
         <v>1361</v>
       </c>
       <c r="C581" s="13" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D581" s="25" t="s">
         <v>1423</v>
       </c>
-      <c r="D581" s="25" t="s">
+      <c r="E581" s="13"/>
+    </row>
+    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E582" s="13"/>
+    </row>
+    <row r="583" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A583" s="15" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B583" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C583" s="13" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D583" s="25" t="s">
         <v>1424</v>
       </c>
-      <c r="E581" s="13"/>
-    </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A582" s="13"/>
-      <c r="B582" s="13"/>
-      <c r="C582" s="13"/>
-      <c r="D582" s="14"/>
-      <c r="E582" s="13"/>
-    </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="13"/>
-      <c r="B583" s="13"/>
-      <c r="C583" s="13"/>
-      <c r="D583" s="14"/>
       <c r="E583" s="13"/>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="13"/>
-      <c r="B584" s="13"/>
-      <c r="C584" s="13"/>
-      <c r="D584" s="14"/>
+    <row r="584" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A584" s="15" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B584" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C584" s="13" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D584" s="25" t="s">
+        <v>1427</v>
+      </c>
       <c r="E584" s="13"/>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
@@ -18538,6 +18588,13 @@
       <c r="C966" s="13"/>
       <c r="D966" s="14"/>
       <c r="E966" s="13"/>
+    </row>
+    <row r="967" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A967" s="13"/>
+      <c r="B967" s="13"/>
+      <c r="C967" s="13"/>
+      <c r="D967" s="14"/>
+      <c r="E967" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
